--- a/hardware/devBoard/manufacture/devBoard BOM JLC.xlsx
+++ b/hardware/devBoard/manufacture/devBoard BOM JLC.xlsx
@@ -5,10 +5,10 @@
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chris\Documents\GitHub\Embedded-Systems-Instructor\Manufacturing Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chris\Documents\GitHub\Embedded-Systems-Instructor\hardware\devBoard\manufacture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29A5197E-1E96-4F2B-BFCC-92875C678E07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1F3AB37-D88A-419E-961A-4F949FF4C626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -254,9 +254,6 @@
     <t>C131974</t>
   </si>
   <si>
-    <t>C132162</t>
-  </si>
-  <si>
     <t>C962159</t>
   </si>
   <si>
@@ -308,10 +305,13 @@
     <t>C883127</t>
   </si>
   <si>
-    <t>C25168846</t>
-  </si>
-  <si>
-    <t>C3039330</t>
+    <t>C69082</t>
+  </si>
+  <si>
+    <t>C5342990</t>
+  </si>
+  <si>
+    <t>C91144</t>
   </si>
 </sst>
 </file>
@@ -935,7 +935,7 @@
         <v>53</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -949,7 +949,7 @@
         <v>54</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -963,7 +963,7 @@
         <v>54</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -977,7 +977,7 @@
         <v>54</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -991,7 +991,7 @@
         <v>54</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1005,7 +1005,7 @@
         <v>54</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1019,7 +1019,7 @@
         <v>54</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1033,7 +1033,7 @@
         <v>54</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1047,7 +1047,7 @@
         <v>54</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -1062,7 +1062,7 @@
         <v>54</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1165,7 +1165,7 @@
         <v>63</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1179,7 +1179,7 @@
         <v>64</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1207,7 +1207,7 @@
         <v>1</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1221,7 +1221,7 @@
         <v>1</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1235,7 +1235,7 @@
         <v>62</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1249,7 +1249,7 @@
         <v>66</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1263,7 +1263,7 @@
         <v>66</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1288,7 +1288,7 @@
         <v>65</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1302,7 +1302,7 @@
         <v>2</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">

--- a/hardware/devBoard/manufacture/devBoard BOM JLC.xlsx
+++ b/hardware/devBoard/manufacture/devBoard BOM JLC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chris\Documents\GitHub\Embedded-Systems-Instructor\hardware\devBoard\manufacture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1F3AB37-D88A-419E-961A-4F949FF4C626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08079872-12A6-4549-8C5E-9C32BA50E710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -269,9 +269,6 @@
     <t>C51680</t>
   </si>
   <si>
-    <t>C18536</t>
-  </si>
-  <si>
     <t>C25379</t>
   </si>
   <si>
@@ -312,6 +309,9 @@
   </si>
   <si>
     <t>C91144</t>
+  </si>
+  <si>
+    <t>Quantity</t>
   </si>
 </sst>
 </file>
@@ -917,14 +917,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECAE32E7-7895-42B0-B9C6-999EBEE1184D}">
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="26.109375" style="1" customWidth="1"/>
     <col min="3" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>52</v>
       </c>
@@ -935,10 +935,13 @@
         <v>53</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -949,10 +952,13 @@
         <v>54</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -963,10 +969,13 @@
         <v>54</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -977,10 +986,13 @@
         <v>54</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -991,10 +1003,13 @@
         <v>54</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
@@ -1005,10 +1020,13 @@
         <v>54</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
@@ -1019,10 +1037,13 @@
         <v>54</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
@@ -1033,10 +1054,13 @@
         <v>54</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -1047,11 +1071,14 @@
         <v>54</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>11</v>
       </c>
@@ -1062,10 +1089,13 @@
         <v>54</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
@@ -1078,8 +1108,11 @@
       <c r="D12" s="1" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E12" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>13</v>
       </c>
@@ -1092,8 +1125,11 @@
       <c r="D13" s="2" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E13" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>14</v>
       </c>
@@ -1106,8 +1142,11 @@
       <c r="D14" s="2" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E14" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>15</v>
       </c>
@@ -1120,8 +1159,14 @@
       <c r="D15" s="2" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="E15" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>56</v>
       </c>
@@ -1132,10 +1177,13 @@
         <v>58</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>59</v>
       </c>
@@ -1146,15 +1194,19 @@
         <v>61</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="4"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>50</v>
       </c>
@@ -1167,8 +1219,11 @@
       <c r="D20" s="1" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E20" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>16</v>
       </c>
@@ -1179,10 +1234,13 @@
         <v>64</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>17</v>
       </c>
@@ -1195,8 +1253,11 @@
       <c r="D22" s="2" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E22" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1206,11 +1267,11 @@
       <c r="C23" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E23" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>25</v>
       </c>
@@ -1223,8 +1284,11 @@
       <c r="D24" s="1" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E24" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>19</v>
       </c>
@@ -1237,8 +1301,11 @@
       <c r="D25" s="1" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E25" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>20</v>
       </c>
@@ -1251,8 +1318,11 @@
       <c r="D26" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E26" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>21</v>
       </c>
@@ -1265,8 +1335,11 @@
       <c r="D27" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E27" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>22</v>
       </c>
@@ -1276,8 +1349,11 @@
       <c r="C28" s="2" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E28" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>23</v>
       </c>
@@ -1288,10 +1364,13 @@
         <v>65</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+      <c r="E29" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1303,6 +1382,9 @@
       </c>
       <c r="D30" s="1" t="s">
         <v>72</v>
+      </c>
+      <c r="E30" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
